--- a/docs/example/quotation-export.xlsx
+++ b/docs/example/quotation-export.xlsx
@@ -58,15 +58,15 @@
   </numFmts>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
     </font>
     <font>
-      <family val="2"/>
       <b val="1"/>
       <color/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">

--- a/docs/example/quotation-export.xlsx
+++ b/docs/example/quotation-export.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="16" uniqueCount="16">
   <si>
     <t>No. Quotation</t>
   </si>
@@ -28,25 +28,40 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Subtotal</t>
+    <t>Total Produk</t>
   </si>
   <si>
     <t>Diskon</t>
   </si>
   <si>
+    <t>Pengiriman</t>
+  </si>
+  <si>
+    <t>Sub Total</t>
+  </si>
+  <si>
+    <t>PPN</t>
+  </si>
+  <si>
+    <t>Nilai PPN</t>
+  </si>
+  <si>
     <t>Grand Total</t>
   </si>
   <si>
     <t>Q-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-10</t>
+    <t>2026-10-11</t>
   </si>
   <si>
     <t>PT Samudra Contoh Nusantara</t>
   </si>
   <si>
     <t>Disetujui</t>
+  </si>
+  <si>
+    <t>12%</t>
   </si>
 </sst>
 </file>
@@ -388,27 +403,51 @@
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="C2" t="s">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="E2" s="2">
-        <v>17622000</v>
+        <v>17760000</v>
       </c>
       <c r="F2" s="2">
         <v>888000</v>
       </c>
       <c r="G2" s="2">
+        <v>750000</v>
+      </c>
+      <c r="H2" s="2">
+        <v>17622000</v>
+      </c>
+      <c r="I2" t="s">
+        <v>15</v>
+      </c>
+      <c r="J2" s="2">
+        <v>1938420</v>
+      </c>
+      <c r="K2" s="2">
         <v>19560420</v>
       </c>
     </row>

--- a/docs/example/quotation-export.xlsx
+++ b/docs/example/quotation-export.xlsx
@@ -104,13 +104,16 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="false">
-      <alignment/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="true" applyAlignment="true">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -417,37 +420,37 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="s">
+      <c r="A2" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="E2" s="2">
+      <c r="E2" s="3">
         <v>17760000</v>
       </c>
-      <c r="F2" s="2">
+      <c r="F2" s="3">
         <v>888000</v>
       </c>
-      <c r="G2" s="2">
+      <c r="G2" s="3">
         <v>750000</v>
       </c>
-      <c r="H2" s="2">
+      <c r="H2" s="3">
         <v>17622000</v>
       </c>
-      <c r="I2" t="s">
+      <c r="I2" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="J2" s="2">
+      <c r="J2" s="3">
         <v>1938420</v>
       </c>
-      <c r="K2" s="2">
+      <c r="K2" s="3">
         <v>19560420</v>
       </c>
     </row>

--- a/docs/example/quotation-export.xlsx
+++ b/docs/example/quotation-export.xlsx
@@ -52,7 +52,7 @@
     <t>Q-00001/GNS/X/2026</t>
   </si>
   <si>
-    <t>2026-10-11</t>
+    <t>2026-10-12</t>
   </si>
   <si>
     <t>PT Samudra Contoh Nusantara</t>
